--- a/02_DIA_inicio_2026_analisis_assets/rbd_9458_escuela-boroa_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9458_escuela-boroa_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E916AFF-E621-492F-91E3-4027416D7E7F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB655B6A-9FAC-444E-866C-32F5325EED7E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FA16A91-1C9C-4618-868F-485805417CA4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{685819F8-2B5B-4F7F-BA5C-FEA9FC4E4A1C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04974F25-F380-4F91-872C-DDCC8C433C14}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D1D898E-007E-4627-BA35-00D50744840B}"/>
 </file>